--- a/output/pdf_financials_xlsx/CAF.xlsx
+++ b/output/pdf_financials_xlsx/CAF.xlsx
@@ -6100,54 +6100,52 @@
         <v>-0.014743</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.130095</v>
+        <v>4.462343</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.271515</v>
+        <v>4.464343</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.473154</v>
+        <v>4.713039</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1.714927</v>
+        <v>5.102257</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>1.916257</v>
+        <v>4.548904</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>1.631039</v>
+        <v>3.76469</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>1.468974</v>
+        <v>2.836808</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>1.908638</v>
+        <v>3.760242</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>3.59584</v>
+        <v>6.59194</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>3.838286</v>
+        <v>7.214663</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>4.353015</v>
+        <v>7.783595</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>6.72539</v>
+        <v>13.188035</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>7.321446</v>
+        <v>15.140762</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>10.094281</v>
+        <v>20.942552</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>13.196071</v>
-      </c>
-      <c r="S91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.056626</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>-1.676138</v>
       </c>
     </row>
     <row r="92">
@@ -10748,7 +10746,11 @@
           <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -16678,7 +16680,11 @@
           <t>Foreign Currency Translation Reserve total</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CAF.xlsx
+++ b/output/pdf_financials_xlsx/CAF.xlsx
@@ -1059,58 +1059,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.013042</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009405</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.145134</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013572</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0179</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011944</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.007887</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.042384</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.02928</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.017962</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.101284</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.173085</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.151798</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.177718</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.256562</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.5225030000000001</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.7339639999999999</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.779288</v>
       </c>
     </row>
     <row r="13">
@@ -2064,58 +2064,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.273168</v>
+        <v>-3.28621</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.574327</v>
+        <v>-0.583732</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.116062</v>
+        <v>0.970928</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.011998</v>
+        <v>1.02557</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.621424</v>
+        <v>0.639324</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.163899</v>
+        <v>1.151955</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.755569</v>
+        <v>0.747682</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.296631</v>
+        <v>0.254247</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.312218</v>
+        <v>-0.341498</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.736284</v>
+        <v>0.718322</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.697267</v>
+        <v>0.595983</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.730337</v>
+        <v>0.557252</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.546322</v>
+        <v>0.394524</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.597871</v>
+        <v>0.420153</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.821578</v>
+        <v>0.565016</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.558347</v>
+        <v>3.035844</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>3.373244</v>
+        <v>2.63928</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>3.683277</v>
+        <v>2.903989</v>
       </c>
     </row>
     <row r="28">
@@ -2186,58 +2186,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.273168</v>
+        <v>-3.28621</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.574327</v>
+        <v>-0.583732</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.116062</v>
+        <v>0.970928</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.021239</v>
+        <v>1.034811</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.625872</v>
+        <v>0.643772</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.163899</v>
+        <v>1.151955</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.755569</v>
+        <v>0.747682</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.296631</v>
+        <v>0.254247</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.312218</v>
+        <v>-0.341498</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.736284</v>
+        <v>0.718322</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.697267</v>
+        <v>0.595983</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.730337</v>
+        <v>0.557252</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.738842</v>
+        <v>0.587044</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.7853520000000001</v>
+        <v>0.607634</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.036913</v>
+        <v>0.780351</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.781712</v>
+        <v>3.259209</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>3.578662</v>
+        <v>2.844698</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>3.896494</v>
+        <v>3.117206</v>
       </c>
     </row>
     <row r="30">
@@ -2247,58 +2247,58 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-36.21403220062142</v>
+        <v>-36.35832769903779</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-12.59097775976193</v>
+        <v>-12.79716368838894</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>9.452238485022464</v>
+        <v>8.22305840337355</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>7.657344662951362</v>
+        <v>7.759108776704926</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.751403638681377</v>
+        <v>5.915894341464687</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7.775067030701422</v>
+        <v>7.695278835493162</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>5.69930024566229</v>
+        <v>5.639808152898375</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.239416454887103</v>
+        <v>2.776553749964371</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-6.6379534681201</v>
+        <v>-7.26046491059477</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.881726781752176</v>
+        <v>6.713843768602587</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>4.751828071773242</v>
+        <v>4.061584371122729</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>6.215448901522082</v>
+        <v>4.742428948924926</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>5.45606386569689</v>
+        <v>4.335094047136147</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>5.528760321828154</v>
+        <v>4.27765224942921</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.686113000928533</v>
+        <v>3.526634313956506</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11.74760774925254</v>
+        <v>10.12449094612007</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>11.00291664784762</v>
+        <v>8.746278632153251</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>103.7656068080356</v>
+        <v>83.01277305589318</v>
       </c>
     </row>
     <row r="31">
@@ -2437,60 +2437,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.377539</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.581487</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.956894</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.208915</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.429103</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.31373</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.453965</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.881322</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.380562</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.453609</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.552351</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.390916</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.047774</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.780717</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.678158</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>5.300956</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.634628</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>9.592376</v>
       </c>
     </row>
     <row r="35">
@@ -2563,60 +2561,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.377539</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.581487</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.956894</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.208915</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.429103</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.31373</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.453965</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.881322</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.380562</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.453609</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.552351</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.390916</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.047774</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.780717</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.678158</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>5.300956</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.634628</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>9.592376</v>
       </c>
     </row>
     <row r="37">
@@ -3311,55 +3307,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.377539</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.25098</v>
+        <v>0.669493</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.956894</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.246511</v>
+        <v>0.037596</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.465096</v>
+        <v>0.035993</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.347189</v>
+        <v>0.033459</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.48647</v>
+        <v>0.032505</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.908083</v>
+        <v>0.026761</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.407782</v>
+        <v>0.02722</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.489829</v>
+        <v>0.03622</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.574247</v>
+        <v>0.021896</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.456291</v>
+        <v>0.065375</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.069631</v>
+        <v>0.021857</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.875787</v>
+        <v>0.09507</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.678158</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.567141</v>
+        <v>0.266185</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>8.016294</v>
+        <v>0.381666</v>
       </c>
       <c r="S48" s="1" t="inlineStr">
         <is>
@@ -9030,7 +9026,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -33690,7 +33686,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -49088,7 +49084,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" s="5" t="n">

--- a/output/pdf_financials_xlsx/CAF.xlsx
+++ b/output/pdf_financials_xlsx/CAF.xlsx
@@ -1385,7 +1385,7 @@
         <v>-0.343219</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.5818489999999999</v>
+        <v>0.168189</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0.133063</v>
@@ -2329,7 +2329,7 @@
         <v>45.42523581565681</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>196.152458778752</v>
+        <v>56.69973805839579</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-42.61861904182334</v>
@@ -4496,7 +4496,7 @@
         <v>0.310304</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0</v>
@@ -7252,19 +7252,19 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.001124</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.003727</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.004955</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.006236</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.001114</v>
       </c>
     </row>
     <row r="111">
@@ -9427,15 +9427,11 @@
       <c r="H6" s="5" t="n">
         <v>0.034134</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="5" t="n">
+        <v>0.035993</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.033459</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -15830,12 +15826,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Due to Related Party 12(a)</t>
+          <t>Intangible Assets 2(g)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -15849,23 +15845,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G70" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.003462</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-06</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -15936,38 +15926,36 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NON-CURRENT</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Intangible Assets 2(g)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.146806</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.053173</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.291857</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.117247</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08304599999999999</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0.01625</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -16043,33 +16031,35 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Income Tax Payable</t>
+          <t>Due to Related Parties 12</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IncomeTaxPayable</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0.146806</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.053173</v>
+          <t>OtherPayable</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.291857</v>
+        <v>0.796841</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.117247</v>
+        <v>0.694898</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.08304599999999999</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.310304</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.08799999999999999</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -16140,17 +16130,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Due to Related Parties 12</t>
+          <t>Accumulated Other Comprehensive Loss –</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OtherPayable</t>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -16163,19 +16153,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n">
-        <v>0.796841</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.694898</v>
+        <v>-0.271515</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.310304</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.473154</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.753894</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -16246,15 +16236,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NON-CURRENT</t>
+          <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Debentures 10</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -16266,20 +16260,16 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.184611</v>
+        <v>-7.472038</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.897272</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-6.449179</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-5.610642</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -16350,15 +16340,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Reserve for Stock Options</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Foreign Currency Translation Reserve total</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -16370,20 +16364,16 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.120285</v>
+        <v>0.72771</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.120285</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.030961</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>1.15713</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>1.714927</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -16454,19 +16444,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Accumulated Other Comprehensive Loss –</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
-        </is>
-      </c>
+          <t>Due to Related Party 12(a)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16483,10 +16469,12 @@
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>-0.271515</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>-0.473154</v>
+        <v>0.003462</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -16562,19 +16550,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Reserve</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
+          <t>Debentures 10</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -16586,13 +16570,15 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-7.472038</v>
+        <v>0.184611</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>-6.897272</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>-6.449179</v>
+        <v>0.15</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -16668,19 +16654,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Reserve</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Reserve total</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
-        </is>
-      </c>
+          <t>Reserve for Stock Options</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16692,13 +16674,15 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.72771</v>
+        <v>0.120285</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>1.030961</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>1.15713</v>
+        <v>0.120285</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -21350,7 +21334,11 @@
           <t>Accretion 19</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -23672,7 +23660,11 @@
           <t>Accretion 18</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -24286,7 +24278,11 @@
           <t>Accretion 17</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -24890,7 +24886,11 @@
           <t>Deferred Tax Expense (Recovery)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -27216,7 +27216,11 @@
           <t>Deferred Tax Expenses</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -27426,7 +27430,11 @@
           <t>Deferred Tax Expense</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -28276,7 +28284,11 @@
           <t>Deferred Income Tax Expense (Recovery)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28692,7 +28704,11 @@
           <t>Deferred Tax Recovery</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -29422,7 +29438,11 @@
           <t>Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E201" s="5" t="n">
         <v>-1.010336</v>
       </c>
@@ -43890,7 +43910,11 @@
           <t>Income Tax Recovery (Expense) 12(a)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
